--- a/Source data/Fig.3E and S5.xlsx
+++ b/Source data/Fig.3E and S5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GITHUB\HGT_and_fitness\Source data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\HGT_and_fitness\Source data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F54CED3A-9A54-4ECA-AEB4-6F9C476B7019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE76EA8A-5681-43C5-870C-16982EAA9A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="3300" windowWidth="16140" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -426,9 +426,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>15</v>
       </c>
@@ -439,7 +439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -450,10 +450,10 @@
         <v>0.377748639579854</v>
       </c>
       <c r="D2" s="1">
-        <v>6.3965980000000006E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.5039E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -464,10 +464,10 @@
         <v>2.3301959579613598</v>
       </c>
       <c r="D3" s="1">
-        <v>7.7978220000000001E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.4298E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -478,10 +478,10 @@
         <v>2.18236084033596</v>
       </c>
       <c r="D4" s="1">
-        <v>7.8639650000000005E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.5055000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -492,10 +492,10 @@
         <v>2.00267551729051</v>
       </c>
       <c r="D5" s="1">
-        <v>8.2387326999999996E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.4246999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -506,10 +506,10 @@
         <v>1.88580493745591</v>
       </c>
       <c r="D6" s="1">
-        <v>9.9336138000000004E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.5834000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -520,10 +520,10 @@
         <v>2.4946055673725098</v>
       </c>
       <c r="D7" s="1">
-        <v>8.3683300000000002E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.5605000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -534,10 +534,10 @@
         <v>2.34677044974711</v>
       </c>
       <c r="D8" s="1">
-        <v>8.4344730000000007E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.5454000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -548,10 +548,10 @@
         <v>2.16708512670166</v>
       </c>
       <c r="D9" s="1">
-        <v>8.8092406999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.4985999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -562,10 +562,10 @@
         <v>2.0502145468670601</v>
       </c>
       <c r="D10" s="1">
-        <v>0.10504121800000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.6504000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -576,10 +576,10 @@
         <v>0.39941681197939999</v>
       </c>
       <c r="D11" s="1">
-        <v>7.4183570000000004E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.0874999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -590,10 +590,10 @@
         <v>0.55733000823772505</v>
       </c>
       <c r="D12" s="1">
-        <v>6.8562647000000004E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.1013999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -604,10 +604,10 @@
         <v>0.88438772853321301</v>
       </c>
       <c r="D13" s="1">
-        <v>8.5511457999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.2658000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -618,10 +618,10 @@
         <v>0.201801758750669</v>
       </c>
       <c r="D14" s="1">
-        <v>7.8592677E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.2251E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
@@ -632,10 +632,10 @@
         <v>0.52526225112843306</v>
       </c>
       <c r="D15" s="1">
-        <v>9.5541487999999994E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.2616E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -646,7 +646,7 @@
         <v>0.51478641574617301</v>
       </c>
       <c r="D16" s="1">
-        <v>8.3647385000000005E-2</v>
+        <v>1.2404999999999999E-2</v>
       </c>
     </row>
   </sheetData>
